--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N110_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N110_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.57580226757828</v>
+        <v>10.00606786848147</v>
       </c>
       <c r="D2" t="n">
-        <v>29.92266367948493</v>
+        <v>4.862432847916301</v>
       </c>
       <c r="E2" t="n">
-        <v>17.53989800062929</v>
+        <v>2.850233425102259</v>
       </c>
       <c r="F2" t="n">
-        <v>14.12434922280333</v>
+        <v>2.295206748705541</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>96.65559826883685</v>
+        <v>15.70653471868599</v>
       </c>
       <c r="D3" t="n">
-        <v>58.17136212509158</v>
+        <v>9.452846345327382</v>
       </c>
       <c r="E3" t="n">
-        <v>17.53989800062929</v>
+        <v>2.850233425102259</v>
       </c>
       <c r="F3" t="n">
-        <v>14.12434922280333</v>
+        <v>2.295206748705541</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
